--- a/product-definitions/spreadsheet/size-concentration-spectra.xlsx
+++ b/product-definitions/spreadsheet/size-concentration-spectra.xlsx
@@ -179,7 +179,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -200,14 +200,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -230,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -254,30 +249,29 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1748,7 +1742,7 @@
       <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1756,7 +1750,7 @@
       <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1792,23 +1786,23 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>36</v>
       </c>
@@ -1816,7 +1810,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="4" t="s">
         <v>29</v>
       </c>
@@ -1824,28 +1818,29 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26">
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>2</v>
       </c>
@@ -1853,7 +1848,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="4" t="s">
         <v>17</v>
       </c>
@@ -1861,7 +1856,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="4" t="s">
         <v>18</v>
       </c>
@@ -1869,7 +1864,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>20</v>
       </c>
@@ -1877,23 +1872,23 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="B33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="B34" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="4" t="s">
         <v>36</v>
       </c>
@@ -1901,7 +1896,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>29</v>
       </c>
@@ -1909,28 +1904,29 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38">
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="B39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="B40" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
@@ -1938,7 +1934,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="4" t="s">
         <v>17</v>
       </c>
@@ -1946,7 +1942,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="4" t="s">
         <v>18</v>
       </c>
@@ -1954,7 +1950,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="B44" s="4" t="s">
         <v>20</v>
       </c>
@@ -1962,23 +1958,23 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="B45" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="B46" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="B47" s="4" t="s">
         <v>36</v>
       </c>
@@ -1986,7 +1982,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="B48" s="4" t="s">
         <v>29</v>
       </c>
@@ -1994,7 +1990,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50">
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="10" t="s">
         <v>44</v>
       </c>
@@ -2003,7 +2000,7 @@
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="10" t="s">
         <v>14</v>
@@ -2014,18 +2011,18 @@
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="10" t="s">
         <v>2</v>
@@ -2036,7 +2033,7 @@
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="10" t="s">
         <v>17</v>
@@ -2045,7 +2042,7 @@
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="10" t="s">
         <v>18</v>
@@ -2056,23 +2053,23 @@
       <c r="D55" s="10"/>
       <c r="E55" s="10"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="14" t="s">
         <v>48</v>
       </c>
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="16" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="10"/>
